--- a/data/mapas/Mapa_de_Carrera_Ciencias_de_la_Administracion.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Ciencias_de_la_Administracion.xlsx
@@ -555,13 +555,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B34, "SI")</f>
+        <f>COUNTIF(B6:B41, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C34, "SI")</f>
+        <f>COUNTIF(C6:C41, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F34, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F41, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Teoría de la Administración I (Fundamentos y Escuelas)</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B34, "SI")/24</f>
+        <f>COUNTIF(B6:B41, "SI")/32</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Principios de Economía y Mercado</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C34, "SI")/24</f>
+        <f>COUNTIF(C6:C41, "SI")/32</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Introducción a la Disciplina</t>
+          <t>Matemática Aplicada a la Administración</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente I</t>
+          <t>Sistemas de Información y Contabilidad Básica</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -831,10 +831,37 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Pedagogía</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E10" s="10">
+        <f>IF(B10="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F10" s="10">
+        <f>IF(C10="SI", "APROBADO", IF(B10="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
+        <f>IF(C10="SI", "🟢 Aprobada", IF(B10="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
@@ -845,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -860,7 +887,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E11" s="10">
@@ -884,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Sociología de la Educación</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -899,7 +926,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E12" s="10">
@@ -921,37 +948,10 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Sujetos de la Educación</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E13" s="10">
-        <f>IF(B13="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F13" s="10">
-        <f>IF(C13="SI", "APROBADO", IF(B13="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G13" s="11">
-        <f>IF(C13="SI", "🟢 Aprobada", IF(B13="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente II</t>
+          <t>Teoría de la Administración II (Procesos Organizacionales)</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -999,10 +999,37 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Contabilidad Financiera y de Costos</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E15" s="10">
+        <f>IF(B15="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F15" s="10">
+        <f>IF(C15="SI", "APROBADO", IF(B15="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G15" s="11">
+        <f>IF(C15="SI", "🟢 Aprobada", IF(B15="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -1013,7 +1040,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Estadística Aplicada a las Organizaciones</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1028,7 +1055,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E16" s="10">
@@ -1047,7 +1074,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Residencia I</t>
+          <t>Derecho Aplicado a las Organizaciones</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1062,7 +1089,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E17" s="10">
@@ -1081,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Espacio de Definición Institucional</t>
+          <t>Didáctica General</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1096,7 +1123,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E18" s="10">
@@ -1115,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente III</t>
+          <t>Psicología Educacional</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1130,7 +1157,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E19" s="10">
@@ -1146,17 +1173,44 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Sujetos de la Educación</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E20" s="10">
+        <f>IF(B20="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F20" s="10">
+        <f>IF(C20="SI", "APROBADO", IF(B20="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G20" s="11">
+        <f>IF(C20="SI", "🟢 Aprobada", IF(B20="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Residencia II / Taller de Cierre</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1171,7 +1225,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E21" s="10">
@@ -1187,44 +1241,17 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Ética y Trabajo Docente</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E22" s="10">
-        <f>IF(B22="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F22" s="10">
-        <f>IF(C22="SI", "APROBADO", IF(B22="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G22" s="11">
-        <f>IF(C22="SI", "🟢 Aprobada", IF(B22="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Investigación Educativa</t>
+          <t>Administración de Recursos Humanos y Relaciones Laborales</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1239,7 +1266,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E23" s="10">
@@ -1258,7 +1285,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente IV</t>
+          <t>Administración Financiera y Presupuestaria</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1273,7 +1300,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E24" s="10">
@@ -1289,17 +1316,44 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>📌 5° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Comercialización y Marketing Estratégico</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E25" s="10">
+        <f>IF(B25="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F25" s="10">
+        <f>IF(C25="SI", "APROBADO", IF(B25="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G25" s="11">
+        <f>IF(C25="SI", "🟢 Aprobada", IF(B25="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Especialización Superior I</t>
+          <t>Didáctica de la Administración I</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1314,7 +1368,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1333,7 +1387,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Taller de Investigación Aplicada</t>
+          <t>Historia Social de la Educación</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1348,7 +1402,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E27" s="10">
@@ -1367,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de Nivel Superior</t>
+          <t>Derechos Humanos, Sociedad y Estado</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1382,7 +1436,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E28" s="10">
@@ -1401,7 +1455,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Nivel Superior I</t>
+          <t>Construcción de la Práctica Docente I</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1416,7 +1470,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E29" s="10">
@@ -1435,14 +1489,14 @@
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>📌 6° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
+          <t>📌 4° AÑO</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Especialización Superior II</t>
+          <t>Planeamiento Estratégico y Dirección General</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1457,7 +1511,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E31" s="10">
@@ -1476,7 +1530,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Tesis / Trabajo Final de Licenciatura</t>
+          <t>Gestión de Organizaciones Públicas, Privadas y del Tercer Sector</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1491,7 +1545,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1510,7 +1564,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Nivel Superior II</t>
+          <t>Emprendedorismo y Formulación de Proyectos</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1525,7 +1579,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1544,7 +1598,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Acreditación de Residencia Superior</t>
+          <t>Didáctica de la Administración II</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1559,7 +1613,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1575,27 +1629,237 @@
         <v/>
       </c>
     </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Educación Sexual Integral (ESI)</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E35" s="10">
+        <f>IF(B35="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F35" s="10">
+        <f>IF(C35="SI", "APROBADO", IF(B35="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G35" s="11">
+        <f>IF(C35="SI", "🟢 Aprobada", IF(B35="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Ética y Trabajo Docente</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E36" s="10">
+        <f>IF(B36="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F36" s="10">
+        <f>IF(C36="SI", "APROBADO", IF(B36="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G36" s="11">
+        <f>IF(C36="SI", "🟢 Aprobada", IF(B36="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Residencia y Construcción de la Práctica Docente II</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E37" s="10">
+        <f>IF(B37="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F37" s="10">
+        <f>IF(C37="SI", "APROBADO", IF(B37="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G37" s="11">
+        <f>IF(C37="SI", "🟢 Aprobada", IF(B37="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Seminario de Innovación y Gestión Tecnológica</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E39" s="10">
+        <f>IF(B39="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F39" s="10">
+        <f>IF(C39="SI", "APROBADO", IF(B39="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G39" s="11">
+        <f>IF(C39="SI", "🟢 Aprobada", IF(B39="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Seminario de Responsabilidad Social Organizacional</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E40" s="10">
+        <f>IF(B40="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F40" s="10">
+        <f>IF(C40="SI", "APROBADO", IF(B40="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G40" s="11">
+        <f>IF(C40="SI", "🟢 Aprobada", IF(B40="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Taller de Simulación de Negocios y Práctica Profesional</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E41" s="10">
+        <f>IF(B41="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F41" s="10">
+        <f>IF(C41="SI", "APROBADO", IF(B41="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G41" s="11">
+        <f>IF(C41="SI", "🟢 Aprobada", IF(B41="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="I14:J14"/>
+  <mergeCells count="15">
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="A22:G22"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B11 B12 B13 B14 B16 B17 B18 B19 B21 B22 B23 B24 B26 B27 B28 B29 B31 B32 B33 B34 C6 C7 C8 C9 C11 C12 C13 C14 C16 C17 C18 C19 C21 C22 C23 C24 C26 C27 C28 C29 C31 C32 C33 C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B23 B24 B25 B26 B27 B28 B29 B31 B32 B33 B34 B35 B36 B37 B39 B40 B41 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C23 C24 C25 C26 C27 C28 C29 C31 C32 C33 C34 C35 C36 C37 C39 C40 C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/mapas/Mapa_de_Carrera_Ciencias_de_la_Administracion.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Ciencias_de_la_Administracion.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B41, "SI")</f>
+        <f>COUNTIF(B6:B50, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C41, "SI")</f>
+        <f>COUNTIF(C6:C50, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F41, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F50, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Teoría de la Administración I (Fundamentos y Escuelas)</t>
+          <t>Sistemas de Información Contable</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B41, "SI")/32</f>
+        <f>COUNTIF(B6:B50, "SI")/40</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Principios de Economía y Mercado</t>
+          <t>Análisis Matemático</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C41, "SI")/32</f>
+        <f>COUNTIF(C6:C50, "SI")/40</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Matemática Aplicada a la Administración</t>
+          <t>Derecho Público</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Sistemas de Información y Contabilidad Básica</t>
+          <t>Introducción a la Economía</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Historia Económica General y Argentina</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
+          <t>Lectura, escritura y oralidad 1</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo I</t>
+          <t>Pedagogía</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -948,10 +948,37 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Psicología educacional</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E13" s="10">
+        <f>IF(B13="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F13" s="10">
+        <f>IF(C13="SI", "APROBADO", IF(B13="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G13" s="11">
+        <f>IF(C13="SI", "🟢 Aprobada", IF(B13="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -962,7 +989,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Teoría de la Administración II (Procesos Organizacionales)</t>
+          <t>Sujetos de la enseñanza</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -977,7 +1004,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E14" s="10">
@@ -1001,7 +1028,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Contabilidad Financiera y de Costos</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1016,7 +1043,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E15" s="10">
@@ -1037,44 +1064,17 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Estadística Aplicada a las Organizaciones</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E16" s="10">
-        <f>IF(B16="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F16" s="10">
-        <f>IF(C16="SI", "APROBADO", IF(B16="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G16" s="11">
-        <f>IF(C16="SI", "🟢 Aprobada", IF(B16="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Derecho Aplicado a las Organizaciones</t>
+          <t>Pricipios de administración</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1108,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Estadística</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1142,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Derecho civil y societario</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1176,7 +1176,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Sujetos de la Educación</t>
+          <t>Didactica general</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo II</t>
+          <t>Filosofía</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1241,17 +1241,44 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Geografía económica</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E22" s="10">
+        <f>IF(B22="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F22" s="10">
+        <f>IF(C22="SI", "APROBADO", IF(B22="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G22" s="11">
+        <f>IF(C22="SI", "🟢 Aprobada", IF(B22="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Administración de Recursos Humanos y Relaciones Laborales</t>
+          <t>Lectura, escritura y oralidad 2</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1266,7 +1293,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E23" s="10">
@@ -1285,7 +1312,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Administración Financiera y Presupuestaria</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1300,7 +1327,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E24" s="10">
@@ -1316,44 +1343,17 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Comercialización y Marketing Estratégico</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>3° Año</t>
-        </is>
-      </c>
-      <c r="E25" s="10">
-        <f>IF(B25="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F25" s="10">
-        <f>IF(C25="SI", "APROBADO", IF(B25="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G25" s="11">
-        <f>IF(C25="SI", "🟢 Aprobada", IF(B25="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de la Administración I</t>
+          <t>Contabilidad de gestión y costos</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Régimen tributario y laboral</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Derechos Humanos, Sociedad y Estado</t>
+          <t>Derecho comercial y Económico</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Construcción de la Práctica Docente I</t>
+          <t>Didáctica Específica de las Ciencias de la Administración y Constr. de la Práctica Docente</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1486,17 +1486,44 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Historia de la educación Argentina</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E30" s="10">
+        <f>IF(B30="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F30" s="10">
+        <f>IF(C30="SI", "APROBADO", IF(B30="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G30" s="11">
+        <f>IF(C30="SI", "🟢 Aprobada", IF(B30="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Planeamiento Estratégico y Dirección General</t>
+          <t>DD HH, sociedad y estado</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E31" s="10">
@@ -1530,7 +1557,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Gestión de Organizaciones Públicas, Privadas y del Tercer Sector</t>
+          <t>Matemática financiera</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1545,7 +1572,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1561,44 +1588,17 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>Emprendedorismo y Formulación de Proyectos</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E33" s="10">
-        <f>IF(B33="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F33" s="10">
-        <f>IF(C33="SI", "APROBADO", IF(B33="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G33" s="11">
-        <f>IF(C33="SI", "🟢 Aprobada", IF(B33="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de la Administración II</t>
+          <t>Administración estratégica</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1632,7 +1632,7 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Educación Sexual Integral (ESI)</t>
+          <t>Taller diseño y gestión de organizaciones</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Ética y Trabajo Docente</t>
+          <t>Taller de nuevas tecnologias</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1700,7 +1700,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Residencia y Construcción de la Práctica Docente II</t>
+          <t>Metodología de la investigación</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1731,17 +1731,44 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
-        </is>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Sistema y política educativa</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E38" s="10">
+        <f>IF(B38="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F38" s="10">
+        <f>IF(C38="SI", "APROBADO", IF(B38="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G38" s="11">
+        <f>IF(C38="SI", "🟢 Aprobada", IF(B38="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Innovación y Gestión Tecnológica</t>
+          <t>Aplicativos informáticos</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -1756,7 +1783,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E39" s="10">
@@ -1775,7 +1802,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Responsabilidad Social Organizacional</t>
+          <t>Didáctica de la educación superior</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1790,7 +1817,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E40" s="10">
@@ -1809,7 +1836,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Taller de Simulación de Negocios y Práctica Profesional</t>
+          <t>Didactica de educación a distancia</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1824,7 +1851,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E41" s="10">
@@ -1840,26 +1867,279 @@
         <v/>
       </c>
     </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Comercialización y marketing</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E42" s="10">
+        <f>IF(B42="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F42" s="10">
+        <f>IF(C42="SI", "APROBADO", IF(B42="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G42" s="11">
+        <f>IF(C42="SI", "🟢 Aprobada", IF(B42="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Administración de recursos humanos</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E43" s="10">
+        <f>IF(B43="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F43" s="10">
+        <f>IF(C43="SI", "APROBADO", IF(B43="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G43" s="11">
+        <f>IF(C43="SI", "🟢 Aprobada", IF(B43="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>📌 5° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Taller de lengua extranjera - ingles</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E45" s="10">
+        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F45" s="10">
+        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G45" s="11">
+        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Taller de informática</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E46" s="10">
+        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F46" s="10">
+        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G46" s="11">
+        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Esi</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E47" s="10">
+        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F47" s="10">
+        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="11">
+        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Construccion de la practica docente 2</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E48" s="10">
+        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F48" s="10">
+        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G48" s="11">
+        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Taller optativo: Valuación contable</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E50" s="10">
+        <f>IF(B50="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F50" s="10">
+        <f>IF(C50="SI", "APROBADO", IF(B50="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G50" s="11">
+        <f>IF(C50="SI", "🟢 Aprobada", IF(B50="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A13:G13"/>
+  <mergeCells count="16">
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A44:G44"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A22:G22"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A38:G38"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A49:G49"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B23 B24 B25 B26 B27 B28 B29 B31 B32 B33 B34 B35 B36 B37 B39 B40 B41 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C23 C24 C25 C26 C27 C28 C29 C31 C32 C33 C34 C35 C36 C37 C39 C40 C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B17 B18 B19 B20 B21 B22 B23 B24 B26 B27 B28 B29 B30 B31 B32 B34 B35 B36 B37 B38 B39 B40 B41 B42 B43 B45 B46 B47 B48 B50 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C17 C18 C19 C20 C21 C22 C23 C24 C26 C27 C28 C29 C30 C31 C32 C34 C35 C36 C37 C38 C39 C40 C41 C42 C43 C45 C46 C47 C48 C50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
